--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125570730</v>
+        <v>125571453</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603828</v>
+        <v>603768</v>
       </c>
       <c r="R2" t="n">
-        <v>6936534</v>
+        <v>6936599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125571453</v>
+        <v>125571105</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603768</v>
+        <v>603737</v>
       </c>
       <c r="R3" t="n">
-        <v>6936599</v>
+        <v>6936540</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125571105</v>
+        <v>125570730</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603737</v>
+        <v>603828</v>
       </c>
       <c r="R4" t="n">
-        <v>6936540</v>
+        <v>6936534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125571105</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125571105</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571453</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125571105</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125570730</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571453</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125570730</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,6 +984,200 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129924179</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rödmyrhamrarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>603777</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6936577</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129924158</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80090</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rödmyrhamrarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603792</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6936586</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571453</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125570730</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129924179</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129924158</v>
       </c>
       <c r="B6" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>129924179</v>
       </c>
       <c r="B5" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129924158</v>
       </c>
       <c r="B6" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125571453</v>
+        <v>125571105</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603768</v>
+        <v>603737</v>
       </c>
       <c r="R2" t="n">
-        <v>6936599</v>
+        <v>6936540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125571105</v>
+        <v>129924158</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603737</v>
+        <v>603792</v>
       </c>
       <c r="R3" t="n">
-        <v>6936540</v>
+        <v>6936586</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570730</v>
+        <v>129924179</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603828</v>
+        <v>603777</v>
       </c>
       <c r="R4" t="n">
-        <v>6936534</v>
+        <v>6936577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129924179</v>
+        <v>125570730</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +977,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603777</v>
+        <v>603828</v>
       </c>
       <c r="R5" t="n">
-        <v>6936577</v>
+        <v>6936534</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1036,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,45 +1073,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129924158</v>
+        <v>125571453</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödmyrhamrarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603792</v>
+        <v>603768</v>
       </c>
       <c r="R6" t="n">
-        <v>6936586</v>
+        <v>6936599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,12 +1143,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25500-2025 artfynd.xlsx
+++ b/artfynd/A 25500-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571105</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129924158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129924179</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125570730</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125571453</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>